--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260715.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260715.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.96%</t>
+          <t>10.64%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.76%</t>
+          <t>8.62%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.39%</t>
+          <t>7.30%</t>
         </is>
       </c>
     </row>
@@ -682,73 +682,73 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.11%</t>
+          <t>7.00%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>2,443,000</t>
+          <t>16,607,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.86%</t>
+          <t>5.67%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>6,334,000</t>
+          <t>2,443,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.47%</t>
+          <t>5.64%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>16,333,000</t>
+          <t>6,334,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>5.41%</t>
+          <t>5.40%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>4.95%</t>
+          <t>5.24%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>4.65%</t>
+          <t>4.91%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>4.10%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>15,284,000</t>
+          <t>15,770,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>3.71%</t>
+          <t>3.93%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>3.64%</t>
+          <t>3.57%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>3.37%</t>
         </is>
       </c>
     </row>
@@ -924,51 +924,51 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>3.11%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>5,160,000</t>
+          <t>2,267,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.71%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>2,267,000</t>
+          <t>5,160,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.70%</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>416,900</t>
+          <t>448,900</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
@@ -1100,139 +1100,139 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>3,528,000</t>
+          <t>4,119,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>349,000</t>
+          <t>3,528,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>4,334,000</t>
+          <t>349,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>528,000</t>
+          <t>4,334,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>2,966,000</t>
+          <t>528,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>1,886,000</t>
+          <t>2,966,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.24%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.14%</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1393,12 +1393,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>107,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,12 +1437,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1481,12 +1481,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1525,12 +1525,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>富喬</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>107,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>3,212,985,822</t>
+          <t>6,371,960,136</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>-1,418,320,925</t>
+          <t>-2,269,854,099</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
